--- a/לוח זמנים אמא.xlsx
+++ b/לוח זמנים אמא.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://intel-my.sharepoint.com/personal/david_hai_yossef_cohen_intel_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davidhai\יום הולדת אמא\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1E76630-E096-4983-A5F2-ADA726BC4BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2249F86E-44BC-47B8-A8E6-8E5AEFEB7154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8E9FB3A8-0EEF-4272-A0E1-FF7076610F86}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
   <si>
     <t>לידה</t>
   </si>
@@ -159,16 +159,82 @@
   </si>
   <si>
     <t>כט שבט תשסט</t>
+  </si>
+  <si>
+    <t>שישי</t>
+  </si>
+  <si>
+    <t>שירים</t>
+  </si>
+  <si>
+    <t>חמישי</t>
+  </si>
+  <si>
+    <t>מתכונים</t>
+  </si>
+  <si>
+    <t>ראשון</t>
+  </si>
+  <si>
+    <t>שני</t>
+  </si>
+  <si>
+    <t>שלישי</t>
+  </si>
+  <si>
+    <t>רביעי</t>
+  </si>
+  <si>
+    <t>טיולים</t>
+  </si>
+  <si>
+    <t>פודקסטים</t>
+  </si>
+  <si>
+    <t>זוגיות</t>
+  </si>
+  <si>
+    <t>הורות</t>
+  </si>
+  <si>
+    <t>40 מקומות לטייל · המפה של מוריה</t>
+  </si>
+  <si>
+    <t>40 פודקאסטים · האוזניות של מוריה</t>
+  </si>
+  <si>
+    <t>40 שירים · הפלייליסט של מוריה</t>
+  </si>
+  <si>
+    <t>40 עצות לזוגיות טובה · למוריה באהבה</t>
+  </si>
+  <si>
+    <t>40 עצות להורות · למוריה באהבה</t>
+  </si>
+  <si>
+    <t>40 מתכונים · המטבח של מוריה</t>
+  </si>
+  <si>
+    <t>V</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="177"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
@@ -198,14 +264,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -538,14 +607,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2BFAE93-44C3-4361-BA06-77108C7014E3}">
-  <dimension ref="A2:B21"/>
+  <dimension ref="A2:H21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.375" customWidth="1"/>
     <col min="2" max="2" width="23.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -553,7 +622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -561,55 +630,124 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="F6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B9" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -617,7 +755,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -625,7 +763,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>35</v>
       </c>
@@ -633,7 +771,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
@@ -641,7 +779,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -649,7 +787,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -657,7 +795,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
@@ -706,6 +844,14 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" r:id="rId1" display="https://davidhaiintel.github.io/David-Hai-Cohen/travel.html" xr:uid="{ADE713DB-8F04-4239-A79C-B0BACEFDE863}"/>
+    <hyperlink ref="H9" r:id="rId2" display="https://davidhaiintel.github.io/David-Hai-Cohen/podcasts.html" xr:uid="{660C483C-C202-416F-BFA6-F4B8380EB7A0}"/>
+    <hyperlink ref="H5" r:id="rId3" display="https://davidhaiintel.github.io/David-Hai-Cohen/songs.html" xr:uid="{4E8849E2-61F9-4A10-B926-4FF8E7912691}"/>
+    <hyperlink ref="H8" r:id="rId4" display="https://davidhaiintel.github.io/David-Hai-Cohen/couple.html" xr:uid="{CCAF763B-C9AD-4D52-A072-38918D161DDC}"/>
+    <hyperlink ref="H7" r:id="rId5" display="https://davidhaiintel.github.io/David-Hai-Cohen/parenting.html" xr:uid="{E8B435B9-3B0D-4F5E-A2F5-35AE22C9ABF1}"/>
+    <hyperlink ref="H4" r:id="rId6" display="https://davidhaiintel.github.io/David-Hai-Cohen/recipes.html" xr:uid="{9B7037BB-0126-45E3-B676-C43B41BE13FB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/לוח זמנים אמא.xlsx
+++ b/לוח זמנים אמא.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davidhai\יום הולדת אמא\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2249F86E-44BC-47B8-A8E6-8E5AEFEB7154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57C76B4-530E-4F8B-B339-744C6230AAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8E9FB3A8-0EEF-4272-A0E1-FF7076610F86}"/>
+    <workbookView xWindow="1125" yWindow="4305" windowWidth="21600" windowHeight="11175" xr2:uid="{8E9FB3A8-0EEF-4272-A0E1-FF7076610F86}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
   <si>
     <t>לידה</t>
   </si>
@@ -677,6 +677,9 @@
       <c r="B6" t="s">
         <v>39</v>
       </c>
+      <c r="E6" t="s">
+        <v>58</v>
+      </c>
       <c r="F6" t="s">
         <v>44</v>
       </c>

--- a/לוח זמנים אמא.xlsx
+++ b/לוח זמנים אמא.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davidhai\יום הולדת אמא\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57C76B4-530E-4F8B-B339-744C6230AAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BFD3C1-E321-4899-AD9F-F6437392B738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1125" yWindow="4305" windowWidth="21600" windowHeight="11175" xr2:uid="{8E9FB3A8-0EEF-4272-A0E1-FF7076610F86}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
   <si>
     <t>לידה</t>
   </si>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t>V</t>
+  </si>
+  <si>
+    <t>💛 יום הולדת 40 למוריה 💛</t>
   </si>
 </sst>
 </file>
@@ -629,6 +632,9 @@
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="H3" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -854,6 +860,7 @@
     <hyperlink ref="H8" r:id="rId4" display="https://davidhaiintel.github.io/David-Hai-Cohen/couple.html" xr:uid="{CCAF763B-C9AD-4D52-A072-38918D161DDC}"/>
     <hyperlink ref="H7" r:id="rId5" display="https://davidhaiintel.github.io/David-Hai-Cohen/parenting.html" xr:uid="{E8B435B9-3B0D-4F5E-A2F5-35AE22C9ABF1}"/>
     <hyperlink ref="H4" r:id="rId6" display="https://davidhaiintel.github.io/David-Hai-Cohen/recipes.html" xr:uid="{9B7037BB-0126-45E3-B676-C43B41BE13FB}"/>
+    <hyperlink ref="H3" r:id="rId7" display="https://davidhaiintel.github.io/David-Hai-Cohen/index.html" xr:uid="{120ADC74-94D3-497D-A6E1-D348D2651DF9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
